--- a/product_db.xlsx
+++ b/product_db.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
         <v>11000</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         <v>4500</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
@@ -938,6 +938,24 @@
       </c>
       <c r="D30" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>客製化</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D31" t="n">
+        <v>15000</v>
       </c>
     </row>
   </sheetData>

--- a/product_db.xlsx
+++ b/product_db.xlsx
@@ -503,7 +503,7 @@
         <v>11000</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6">

--- a/product_db.xlsx
+++ b/product_db.xlsx
@@ -503,7 +503,7 @@
         <v>11000</v>
       </c>
       <c r="D5" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="6">

--- a/product_db.xlsx
+++ b/product_db.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="品項" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="贈品" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -961,4 +962,40 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>贈品名稱</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>測試</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>